--- a/docs/design-vi/ACSMS-SCR-021/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_配達手数料支払情報出力画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-021/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_配達手数料支払情報出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,78 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật: ①bổ sung cột「手数料」vào TC-012 (hiển thị grid) và TC-029 (header Excel) — bản v1.1 tiếng Nhật (2026/07/02) đã đổi cột này từ đơn giá phí giao báo sang phân loại bên chịu phí chuyển khoản (nhãn m_code TESURYO_KUBUN) nhưng bản này chưa phản ánh. ②tạo カテゴリ6 và thêm 2 ca (041〜042): giới hạn đối tượng tổng hợp chỉ bản giấy (#56599) và chặn xuất file khi có cửa hàng bán tham chiếu đơn giá phí giao báo hết hiệu lực (HTTP 409 INACTIVE_TANKA_REFERENCED)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ56"/>
+  <dimension ref="A1:BQ59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9050,7 +9108,7 @@
       <c r="BP24" s="10" t="n"/>
       <c r="BQ24" s="11" t="n"/>
     </row>
-    <row r="25" ht="208" customHeight="1">
+    <row r="25" ht="320" customHeight="1">
       <c r="A25" s="44" t="n">
         <v>12</v>
       </c>
@@ -9158,7 +9216,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Các cột対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・備考 được hiển thị
+            <t xml:space="preserve">・Các cột対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・手数料・備考 được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Cột「手数料」hiển thị phân loại bên chịu phí chuyển khoản (m_hanbaiten.furikomi_tesuryo_futan_kubun) bằng nhãn m_code TESURYO_KUBUN (1:JA / 2:販売店), không hiển thị số tiền (¥đơn giá)
 </t>
           </r>
           <r>
@@ -11885,7 +11951,7 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="256" customHeight="1">
+    <row r="44" ht="368" customHeight="1">
       <c r="A44" s="44" t="n">
         <v>29</v>
       </c>
@@ -12001,7 +12067,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dòng header hiển thị対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・備考
+            <t xml:space="preserve">・Dòng header hiển thị対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・手数料・備考
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Cột「手数料」xuất phân loại bên chịu phí chuyển khoản (m_hanbaiten.furikomi_tesuryo_futan_kubun) bằng nhãn m_code TESURYO_KUBUN (1:JA / 2:販売店), không xuất số tiền (¥đơn giá)
 </t>
           </r>
           <r>
@@ -14000,11 +14074,772 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: Giới hạn đối tượng tổng hợp・Chặn xuất file (Scope / Export Gate)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="10" t="n"/>
+      <c r="AM57" s="10" t="n"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="10" t="n"/>
+      <c r="AP57" s="10" t="n"/>
+      <c r="AQ57" s="10" t="n"/>
+      <c r="AR57" s="10" t="n"/>
+      <c r="AS57" s="10" t="n"/>
+      <c r="AT57" s="10" t="n"/>
+      <c r="AU57" s="10" t="n"/>
+      <c r="AV57" s="10" t="n"/>
+      <c r="AW57" s="10" t="n"/>
+      <c r="AX57" s="10" t="n"/>
+      <c r="AY57" s="10" t="n"/>
+      <c r="AZ57" s="10" t="n"/>
+      <c r="BA57" s="10" t="n"/>
+      <c r="BB57" s="10" t="n"/>
+      <c r="BC57" s="10" t="n"/>
+      <c r="BD57" s="10" t="n"/>
+      <c r="BE57" s="10" t="n"/>
+      <c r="BF57" s="10" t="n"/>
+      <c r="BG57" s="10" t="n"/>
+      <c r="BH57" s="10" t="n"/>
+      <c r="BI57" s="10" t="n"/>
+      <c r="BJ57" s="10" t="n"/>
+      <c r="BK57" s="10" t="n"/>
+      <c r="BL57" s="10" t="n"/>
+      <c r="BM57" s="10" t="n"/>
+      <c r="BN57" s="10" t="n"/>
+      <c r="BO57" s="10" t="n"/>
+      <c r="BP57" s="10" t="n"/>
+      <c r="BQ57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="450" customHeight="1">
+      <c r="A58" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-021-041</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>Đối tượng tổng hợp — Giới hạn chỉ bản giấy (#56599)</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `haitatsuryo.export`)
+・Cùng một cửa hàng bán A có thật, gắn với các người đọc đang được giao báo trong năm-tháng đối tượng xuất như sau
+・(a) Bản giấy (dokusya_shubetsu=1) 3 bản ghi
+・(b) Kết hợp (3) 2 bản ghi
+・(c) Bản điện tử (2) 1 bản ghi (ở trạng thái gắn với cửa hàng bán A có thật, không phải cửa hàng dummy)
+・Cửa hàng dummy (9999999999) có thiết lập đơn giá phí giao báo và có người đọc bản điện tử gắn vào</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chỉ định năm-tháng đối tượng xuất, hiển thị preview và kiểm tra số bản・số tiền của cửa hàng bán A
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất Excel và xác nhận số bản・số tiền của dòng cửa hàng bán A khớp với preview
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra xem dòng của cửa hàng dummy có xuất hiện trong preview・Excel hay không
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất với cửa hàng bán B chỉ có (b) kết hợp và (c) bản điện tử gắn vào
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Cho đơn giá phí giao báo mà người đọc (b) hoặc (c) tham chiếu **hết hiệu lực** rồi xuất</t>
+          </r>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Số bản của cửa hàng bán A được tổng hợp **chỉ 3 bản ghi** (chỉ bản giấy). 2 kết hợp・1 bản điện tử không được cộng vào
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Giá trị trong Excel khớp với preview
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Dù cửa hàng dummy có thiết lập đơn giá phí giao báo, nếu chỉ có bản điện tử gắn vào thì số tiền không được cộng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Cửa hàng bán B là 0 bản ghi (hoặc không xuất hiện trong danh sách)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Việc xuất **không bị chặn** (không phát sinh INACTIVE_TANKA_REFERENCED)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Phí giao báo là "đối giá cho việc giao báo giấy", nên bản điện tử (2) vốn không có việc giao báo và kết hợp (3) đều nằm ngoài đối tượng (yêu cầu khách hàng 2026-08 / #56599)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trước đây không lọc theo loại đăng ký, nên kết hợp gắn với cửa hàng bán có thật vẫn được cộng vào, và bản điện tử cũng được cộng nếu cửa hàng dummy có thiết lập đơn giá phí giao báo. Tức là **số tiền thanh toán thay đổi tùy theo tình trạng chỉnh trang master**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Bước 5 là để xác nhận điều kiện loại đăng ký giống nhau đã được đưa vào **cả hai** SQL tổng hợp và SQL kiểm tra đơn giá hết hiệu lực. Nếu chỉ một bên có thì xảy ra bất nhất "số tiền là 0 yên nhưng không xuất được vì lỗi đơn giá hết hiệu lực"
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Xuất dữ liệu trích nợ tài khoản (SCR-020) có điều kiện khác — "bản giấy ＋ bản điện tử đã duyệt・trả phí". Không được dùng lại nguyên điều kiện của màn hình này</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="45" t="inlineStr"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="45" t="inlineStr"/>
+      <c r="AK58" s="10" t="n"/>
+      <c r="AL58" s="11" t="n"/>
+      <c r="AM58" s="45" t="inlineStr"/>
+      <c r="AN58" s="10" t="n"/>
+      <c r="AO58" s="11" t="n"/>
+      <c r="AP58" s="45" t="inlineStr"/>
+      <c r="AQ58" s="10" t="n"/>
+      <c r="AR58" s="11" t="n"/>
+      <c r="AS58" s="45" t="inlineStr"/>
+      <c r="AT58" s="10" t="n"/>
+      <c r="AU58" s="11" t="n"/>
+      <c r="AV58" s="45" t="inlineStr"/>
+      <c r="AW58" s="10" t="n"/>
+      <c r="AX58" s="11" t="n"/>
+      <c r="AY58" s="45" t="inlineStr"/>
+      <c r="AZ58" s="10" t="n"/>
+      <c r="BA58" s="11" t="n"/>
+      <c r="BB58" s="45" t="inlineStr"/>
+      <c r="BC58" s="10" t="n"/>
+      <c r="BD58" s="11" t="n"/>
+      <c r="BE58" s="45" t="inlineStr"/>
+      <c r="BF58" s="10" t="n"/>
+      <c r="BG58" s="11" t="n"/>
+      <c r="BH58" s="45" t="inlineStr"/>
+      <c r="BI58" s="10" t="n"/>
+      <c r="BJ58" s="11" t="n"/>
+      <c r="BK58" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="BL58" s="10" t="n"/>
+      <c r="BM58" s="10" t="n"/>
+      <c r="BN58" s="10" t="n"/>
+      <c r="BO58" s="10" t="n"/>
+      <c r="BP58" s="10" t="n"/>
+      <c r="BQ58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="450" customHeight="1">
+      <c r="A59" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-021-042</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>Chặn xuất file — Khi tồn tại cửa hàng bán tham chiếu đơn giá phí giao báo đã hết hiệu lực (INACTIVE_TANKA_REFERENCED)</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `haitatsuryo.export`)
+・Trong tập đối tượng xuất tồn tại từ 1 cửa hàng bán trở lên có đơn giá phí giao báo (tanka_type=2) với `active_flg = FALSE`
+・Chuẩn bị riêng cả mẫu có từ 20 bản ghi trở lên (để xác nhận việc cắt bớt)</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực hiện **preview** ở trạng thái chỉ có 1 cửa hàng bán tham chiếu đơn giá hết hiệu lực
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực hiện **xuất Excel** ở cùng trạng thái
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra `error_code`・`message`・`errors[]`・`total` của response
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực hiện ở trạng thái có 20 bản ghi và kiểm tra số phần tử của `errors[]` cùng `total`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra hiển thị thông báo trên màn hình và nơi được điều hướng đến
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Đổi đơn giá phí giao báo của cửa hàng bán tương ứng sang đơn giá còn hiệu lực rồi thực hiện lại
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xuất với cửa hàng bán tham chiếu đơn giá có kỳ áp dụng nằm ngoài năm-tháng đối tượng xuất nhưng `active_flg = TRUE`</t>
+          </r>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Preview bị chặn và trả về HTTP status code 409
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Việc xuất cũng bị chặn và file không được sinh ra (kiểm tra ở cả preview lẫn xuất file)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`error_code: INACTIVE_TANKA_REFERENCED`, `message` là `失効した配達手数料単価を参照している販売店が存在するため、配達手数料支払情報を出力できません。該当販売店の単価を変更してから再度実行してください。`. Mỗi phần tử của `errors[]` có dạng `{ field: "&lt;hanbaiten_id&gt;", message: "&lt;mã cửa hàng bán&gt; &lt;tên cửa hàng bán&gt;（単価: &lt;mã đơn giá&gt; &lt;tên đơn giá&gt;）" }`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`errors[]` bị **cắt bớt ở 15 phần tử đầu**. `total` vẫn giữ nguyên là 20
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Được tóm tắt là "hiển thị 15 trong số 20 bản ghi tương ứng". Việc xác nhận toàn bộ・đổi đơn giá được điều hướng đến **màn hình tìm kiếm chi tiết cửa hàng bán (lọc tham chiếu đơn giá phí giao báo hết hiệu lực)**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất thành công
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất thành công (việc đánh giá còn hiệu lực chỉ dựa trên `active_flg`, không đánh giá theo ngày của kỳ áp dụng)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Thông báo có nội dung khác với xuất dữ liệu trích nợ tài khoản (SCR-020) (là "配達手数料単価" chứ không phải "単価", đối tượng là "販売店" chứ không phải "購読者"). Do cài đặt truyền nội dung riêng theo màn hình vào cùng một `InactiveTankaReferencedException`, nên khi kiểm thử hai màn không được nhầm lẫn nội dung
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`errors[].field` là **`hanbaiten_id`** chứ không phải số dòng (SCR-020 là số dòng)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Đơn giá hết hiệu lực mà người đọc ngoài đối tượng tổng hợp (bản điện tử・kết hợp bị loại theo #56599) tham chiếu cũng không nằm trong tập của kiểm tra này (xem ACSMS-TC-021-041 Bước 5)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="45" t="inlineStr"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="45" t="inlineStr"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="45" t="inlineStr"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="11" t="n"/>
+      <c r="AP59" s="45" t="inlineStr"/>
+      <c r="AQ59" s="10" t="n"/>
+      <c r="AR59" s="11" t="n"/>
+      <c r="AS59" s="45" t="inlineStr"/>
+      <c r="AT59" s="10" t="n"/>
+      <c r="AU59" s="11" t="n"/>
+      <c r="AV59" s="45" t="inlineStr"/>
+      <c r="AW59" s="10" t="n"/>
+      <c r="AX59" s="11" t="n"/>
+      <c r="AY59" s="45" t="inlineStr"/>
+      <c r="AZ59" s="10" t="n"/>
+      <c r="BA59" s="11" t="n"/>
+      <c r="BB59" s="45" t="inlineStr"/>
+      <c r="BC59" s="10" t="n"/>
+      <c r="BD59" s="11" t="n"/>
+      <c r="BE59" s="45" t="inlineStr"/>
+      <c r="BF59" s="10" t="n"/>
+      <c r="BG59" s="11" t="n"/>
+      <c r="BH59" s="45" t="inlineStr"/>
+      <c r="BI59" s="10" t="n"/>
+      <c r="BJ59" s="11" t="n"/>
+      <c r="BK59" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
+      <c r="BL59" s="10" t="n"/>
+      <c r="BM59" s="10" t="n"/>
+      <c r="BN59" s="10" t="n"/>
+      <c r="BO59" s="10" t="n"/>
+      <c r="BP59" s="10" t="n"/>
+      <c r="BQ59" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="751">
+  <mergeCells count="786">
+    <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -14043,6 +14878,7 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BE35:BG35"/>
@@ -14081,7 +14917,9 @@
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="BK13:BQ13"/>
+    <mergeCell ref="AM58:AO58"/>
     <mergeCell ref="BE41:BG41"/>
+    <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
@@ -14154,6 +14992,8 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="B24:D24"/>
@@ -14197,6 +15037,7 @@
     <mergeCell ref="E29:I29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="B37:D37"/>
+    <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="AE33:AF33"/>
@@ -14231,12 +15072,14 @@
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
+    <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AM31:AO31"/>
@@ -14259,6 +15102,7 @@
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="AS54:AU54"/>
@@ -14327,15 +15171,19 @@
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
+    <mergeCell ref="BB58:BD58"/>
     <mergeCell ref="J47:P47"/>
+    <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
@@ -14380,7 +15228,9 @@
     <mergeCell ref="BH17:BJ17"/>
     <mergeCell ref="E48:I48"/>
     <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AP11:AR11"/>
@@ -14405,6 +15255,8 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AS58:AU58"/>
+    <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
@@ -14414,13 +15266,16 @@
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="X58:AD58"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
+    <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -14503,6 +15358,7 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="Q58:W58"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
@@ -14515,6 +15371,7 @@
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
+    <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
@@ -14547,8 +15404,10 @@
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="BB45:BD45"/>
+    <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
@@ -14562,6 +15421,7 @@
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
+    <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14570,6 +15430,7 @@
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
+    <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -14592,12 +15453,14 @@
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
     <mergeCell ref="AS24:AU24"/>
+    <mergeCell ref="A57:BQ57"/>
     <mergeCell ref="AS18:AU18"/>
     <mergeCell ref="AM27:AO27"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="AJ46:AL46"/>
@@ -14646,6 +15509,7 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="J15:P15"/>
@@ -14708,6 +15572,7 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
     <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
@@ -14721,6 +15586,7 @@
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
@@ -14731,6 +15597,7 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BE19:BG19"/>
@@ -14753,15 +15620,16 @@
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE27 AE29:AE33 AE35:AE48 AE50:AE56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE27 AE29:AE33 AE35:AE48 AE50:AE56 AE58:AE59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG27 AG29:AG33 AG35:AG48 AG50:AG56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG27 AG29:AG33 AG35:AG48 AG50:AG56 AG58:AG59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV27 AV29:AV33 AV35:AV48 AV50:AV56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV27 AV29:AV33 AV35:AV48 AV50:AV56 AV58:AV59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
